--- a/config/ModbusTCP-点表模板.xlsx
+++ b/config/ModbusTCP-点表模板.xlsx
@@ -1,111 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="point" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'point'!$A$1:$M$6</definedName>
+  </definedNames>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>point-name</t>
-  </si>
-  <si>
-    <t>point-number</t>
-  </si>
-  <si>
-    <t>value-type</t>
-  </si>
-  <si>
-    <t>point-type</t>
-  </si>
-  <si>
-    <t>efficient</t>
-  </si>
-  <si>
-    <t>base-value</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>register-address</t>
-  </si>
-  <si>
-    <t>function-code</t>
-  </si>
-  <si>
-    <t>group-number</t>
-  </si>
-  <si>
-    <t>call-interval</t>
-  </si>
-  <si>
-    <t>user-defined-rule</t>
-  </si>
-  <si>
-    <t>BS.CtrlState</t>
-  </si>
-  <si>
-    <t>DOUBLE</t>
-  </si>
-  <si>
-    <t>DI</t>
-  </si>
-  <si>
-    <t>BIT</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>BS.ActivePW</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>FLOAT</t>
-  </si>
-  <si>
-    <t>BS.Soc</t>
-  </si>
-  <si>
-    <t>BS.SysAPSetPoint</t>
-  </si>
-  <si>
-    <t>AO</t>
-  </si>
-  <si>
-    <t>BS.Stop</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -120,14 +60,87 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -388,259 +401,323 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="13" min="1" width="16"/>
+    <col width="20" customWidth="1" min="1" max="13"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>point-name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>point-number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value-type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>point-type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>efficient</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>base-value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>register-address</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>function-code</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>modbus-value-type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>group-number</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>call-interval</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>user-defined-rule</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>储能SOC</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ESS SOC</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1000</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
+      <c r="I2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>有功功率设定</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>AO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Active Power Setpoint</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>100</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>运行状态</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Running Status</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2000</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>启停控制</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Start Stop Control</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>累计电量</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" t="s">
-        <v>16</v>
-      </c>
+      <c r="F6" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Accumulated Energy</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>